--- a/ig/DM-AVRIL-2025/ValueSet-jdv-j366-statut-bilan-projet-personnalise-ms.xlsx
+++ b/ig/DM-AVRIL-2025/ValueSet-jdv-j366-statut-bilan-projet-personnalise-ms.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -96,13 +96,10 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>ms</t>
+    <t>status</t>
   </si>
   <si>
     <t>=</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
   <si>
     <t/>
@@ -393,23 +390,23 @@
         <v>28</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
